--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119584207</v>
+        <v>119584229</v>
       </c>
       <c r="B6" t="n">
-        <v>102120</v>
+        <v>108787</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,55 +1210,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Etelhem Bare 1:48., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715051</v>
+        <v>714988</v>
       </c>
       <c r="R6" t="n">
-        <v>6364535</v>
+        <v>6364555</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,11 +1274,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7 m hög, fertil.3 stammar: 4 + 5 + 6 cm i diameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1324,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119584107</v>
+        <v>119584224</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>102120</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,25 +1317,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6037533</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1362,9 +1343,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1373,13 +1359,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715005</v>
+        <v>715033</v>
       </c>
       <c r="R7" t="n">
-        <v>6364361</v>
+        <v>6364560</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1413,7 +1399,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Livligt  låtande med revir och lockläte och flygande genom skogsskiftet.</t>
+          <t>3,5 m hög; fertil (några frukter sågs); 2 stammar 1,5 + 3 cm i diameterffrån grövre rot 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,7 +1431,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119584224</v>
+        <v>119584207</v>
       </c>
       <c r="B8" t="n">
         <v>102120</v>
@@ -1499,10 +1485,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715033</v>
+        <v>715051</v>
       </c>
       <c r="R8" t="n">
-        <v>6364560</v>
+        <v>6364535</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1539,7 +1525,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3,5 m hög; fertil (några frukter sågs); 2 stammar 1,5 + 3 cm i diameterffrån grövre rot 4,5 cm i diameter.</t>
+          <t>7 m hög, fertil.3 stammar: 4 + 5 + 6 cm i diameter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,7 +1557,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119584229</v>
+        <v>119584200</v>
       </c>
       <c r="B9" t="n">
         <v>108787</v>
@@ -1611,10 +1597,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>714988</v>
+        <v>715041</v>
       </c>
       <c r="R9" t="n">
-        <v>6364555</v>
+        <v>6364405</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1678,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119584200</v>
+        <v>119584107</v>
       </c>
       <c r="B10" t="n">
-        <v>108787</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1694,34 +1680,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Etelhem Bare 1:48., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715041</v>
+        <v>715005</v>
       </c>
       <c r="R10" t="n">
-        <v>6364405</v>
+        <v>6364361</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1754,6 +1749,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Livligt  låtande med revir och lockläte och flygande genom skogsskiftet.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119584229</v>
+        <v>119584224</v>
       </c>
       <c r="B6" t="n">
-        <v>108787</v>
+        <v>102120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,41 +1210,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Etelhem Bare 1:48., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>714988</v>
+        <v>715033</v>
       </c>
       <c r="R6" t="n">
-        <v>6364555</v>
+        <v>6364560</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,6 +1288,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,5 m hög; fertil (några frukter sågs); 2 stammar 1,5 + 3 cm i diameterffrån grövre rot 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,10 +1324,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119584224</v>
+        <v>119584107</v>
       </c>
       <c r="B7" t="n">
-        <v>102120</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,25 +1336,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6037533</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1343,14 +1362,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1359,13 +1373,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715033</v>
+        <v>715005</v>
       </c>
       <c r="R7" t="n">
-        <v>6364560</v>
+        <v>6364361</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,7 +1413,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3,5 m hög; fertil (några frukter sågs); 2 stammar 1,5 + 3 cm i diameterffrån grövre rot 4,5 cm i diameter.</t>
+          <t>Livligt  låtande med revir och lockläte och flygande genom skogsskiftet.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,10 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119584207</v>
+        <v>119584200</v>
       </c>
       <c r="B8" t="n">
-        <v>102120</v>
+        <v>108787</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,55 +1457,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Etelhem Bare 1:48., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715051</v>
+        <v>715041</v>
       </c>
       <c r="R8" t="n">
-        <v>6364535</v>
+        <v>6364405</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1521,11 +1521,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>7 m hög, fertil.3 stammar: 4 + 5 + 6 cm i diameter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,7 +1552,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119584200</v>
+        <v>119584229</v>
       </c>
       <c r="B9" t="n">
         <v>108787</v>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715041</v>
+        <v>714988</v>
       </c>
       <c r="R9" t="n">
-        <v>6364405</v>
+        <v>6364555</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1664,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119584107</v>
+        <v>119584207</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>102120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,25 +1671,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6037533</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1702,9 +1697,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715005</v>
+        <v>715051</v>
       </c>
       <c r="R10" t="n">
-        <v>6364361</v>
+        <v>6364535</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Livligt  låtande med revir och lockläte och flygande genom skogsskiftet.</t>
+          <t>7 m hög, fertil.3 stammar: 4 + 5 + 6 cm i diameter.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1198,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119584224</v>
+        <v>119584229</v>
       </c>
       <c r="B6" t="n">
-        <v>102120</v>
+        <v>108787</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,55 +1210,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Etelhem Bare 1:48., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715033</v>
+        <v>714988</v>
       </c>
       <c r="R6" t="n">
-        <v>6364560</v>
+        <v>6364555</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,11 +1274,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3,5 m hög; fertil (några frukter sågs); 2 stammar 1,5 + 3 cm i diameterffrån grövre rot 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1324,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119584107</v>
+        <v>119584200</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>108787</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,43 +1321,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Etelhem Bare 1:48., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715005</v>
+        <v>715041</v>
       </c>
       <c r="R7" t="n">
-        <v>6364361</v>
+        <v>6364405</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1409,11 +1381,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Livligt  låtande med revir och lockläte och flygande genom skogsskiftet.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119584200</v>
+        <v>119584107</v>
       </c>
       <c r="B8" t="n">
-        <v>108787</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,34 +1428,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Etelhem Bare 1:48., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715041</v>
+        <v>715005</v>
       </c>
       <c r="R8" t="n">
-        <v>6364405</v>
+        <v>6364361</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1521,6 +1497,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Livligt  låtande med revir och lockläte och flygande genom skogsskiftet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119584229</v>
+        <v>119584224</v>
       </c>
       <c r="B9" t="n">
-        <v>108787</v>
+        <v>102120</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,41 +1545,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Etelhem Bare 1:48., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>714988</v>
+        <v>715033</v>
       </c>
       <c r="R9" t="n">
-        <v>6364555</v>
+        <v>6364560</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1628,6 +1623,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,5 m hög; fertil (några frukter sågs); 2 stammar 1,5 + 3 cm i diameterffrån grövre rot 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,6 +1783,113 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120308319</v>
+      </c>
+      <c r="B11" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Etelhem Bare 1:48., Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>715028</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6364552</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Etelhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalklbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>120308319</v>
       </c>
       <c r="B11" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1890,131 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121391828</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102286</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Etelhem Bare 1:48, körväg 155–195 m N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>714993</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6364507</v>
+      </c>
+      <c r="S12" t="n">
+        <v>44</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Etelhem</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>I-Got-1595</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 träd med koordinater 1666725 6364186 (7 m), 1666707 6364211 (3,5 m)</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>714993</v>
+        <v>715040</v>
       </c>
       <c r="R12" t="n">
-        <v>6364507</v>
+        <v>6364541</v>
       </c>
       <c r="S12" t="n">
         <v>44</v>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,11 +1895,11 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>121391828</v>
       </c>
       <c r="B12" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 34584-2024 artfynd.xlsx
+++ b/artfynd/A 34584-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2015,6 +2015,236 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127282253</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4. Botes tvärväg, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>715009</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6364338</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Etelhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127282272</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4. Botes tvärväg, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>715036</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6364350</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Etelhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
